--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.64975610070089</v>
+        <v>4.330585366363895</v>
       </c>
       <c r="D2" t="n">
-        <v>26.93910189642297</v>
+        <v>4.377604058168733</v>
       </c>
       <c r="E2" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.13775855741751</v>
+        <v>4.572385765580345</v>
       </c>
       <c r="D3" t="n">
-        <v>28.03979959885394</v>
+        <v>4.556467434813765</v>
       </c>
       <c r="E3" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F3" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.38060535466544</v>
+        <v>5.424348370133134</v>
       </c>
       <c r="D4" t="n">
-        <v>5.656854249492381</v>
+        <v>0.9192388155425119</v>
       </c>
       <c r="E4" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F4" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.46489770488125</v>
+        <v>3.000545877043203</v>
       </c>
       <c r="D5" t="n">
-        <v>36.89458808321572</v>
+        <v>5.995370563522554</v>
       </c>
       <c r="E5" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.16495981177415</v>
+        <v>4.4143059694133</v>
       </c>
       <c r="D6" t="n">
-        <v>26.48943848000249</v>
+        <v>4.304533753000405</v>
       </c>
       <c r="E6" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F6" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.99850758723186</v>
+        <v>4.712257482925177</v>
       </c>
       <c r="D7" t="n">
-        <v>12.03274343255758</v>
+        <v>1.955320807790606</v>
       </c>
       <c r="E7" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F7" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.15610199207747</v>
+        <v>5.55036657371259</v>
       </c>
       <c r="D8" t="n">
-        <v>33.56872889661163</v>
+        <v>5.45491844569939</v>
       </c>
       <c r="E8" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F8" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.29445994387846</v>
+        <v>5.41034974088025</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72457280568651</v>
+        <v>5.317743080924059</v>
       </c>
       <c r="E9" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.47420035133488</v>
+        <v>6.577057557091918</v>
       </c>
       <c r="D10" t="n">
-        <v>43.49809221375803</v>
+        <v>7.068439984735679</v>
       </c>
       <c r="E10" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F10" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.2931945147722</v>
+        <v>3.785144108650483</v>
       </c>
       <c r="D11" t="n">
-        <v>20.00033489517281</v>
+        <v>3.250054420465581</v>
       </c>
       <c r="E11" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F11" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.83423369205798</v>
+        <v>4.685562974959422</v>
       </c>
       <c r="D12" t="n">
-        <v>22.82572451091994</v>
+        <v>3.70918023302449</v>
       </c>
       <c r="E12" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F12" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.40012918470192</v>
+        <v>2.177520992514063</v>
       </c>
       <c r="D13" t="n">
-        <v>30.22718179103282</v>
+        <v>4.911917041042833</v>
       </c>
       <c r="E13" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.5643964217143</v>
+        <v>4.966714418528574</v>
       </c>
       <c r="D14" t="n">
-        <v>48.22913537078354</v>
+        <v>7.837234497752325</v>
       </c>
       <c r="E14" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.97996556686354</v>
+        <v>5.034244404615326</v>
       </c>
       <c r="D15" t="n">
-        <v>41.02049436809617</v>
+        <v>6.665830334815627</v>
       </c>
       <c r="E15" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F15" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.07338417016726</v>
+        <v>4.88692492765218</v>
       </c>
       <c r="D16" t="n">
-        <v>43.9429796474816</v>
+        <v>7.14073419271576</v>
       </c>
       <c r="E16" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F16" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.50314448858846</v>
+        <v>5.119260979395625</v>
       </c>
       <c r="D17" t="n">
-        <v>47.30976384223348</v>
+        <v>7.687836624362941</v>
       </c>
       <c r="E17" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F17" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.31089437739344</v>
+        <v>6.388020336326434</v>
       </c>
       <c r="D18" t="n">
-        <v>40.51136085287864</v>
+        <v>6.583096138592779</v>
       </c>
       <c r="E18" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F18" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>34.86064492644694</v>
+        <v>5.664854800547629</v>
       </c>
       <c r="D19" t="n">
-        <v>50.48143840084634</v>
+        <v>8.203233740137531</v>
       </c>
       <c r="E19" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F19" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.96098542403525</v>
+        <v>3.243660131405728</v>
       </c>
       <c r="D20" t="n">
-        <v>19.42301140984918</v>
+        <v>3.156239354100491</v>
       </c>
       <c r="E20" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F20" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>19.15287604343692</v>
+        <v>3.1123423570585</v>
       </c>
       <c r="D21" t="n">
-        <v>18.56233398637902</v>
+        <v>3.01637927278659</v>
       </c>
       <c r="E21" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F21" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>10.36038380291088</v>
+        <v>1.683562367973018</v>
       </c>
       <c r="D22" t="n">
-        <v>9.798317829677718</v>
+        <v>1.592226647322629</v>
       </c>
       <c r="E22" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F22" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>29.00362783809854</v>
+        <v>4.713089523691013</v>
       </c>
       <c r="D23" t="n">
-        <v>28.944264332516</v>
+        <v>4.703442954033849</v>
       </c>
       <c r="E23" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F23" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>14.3958227128836</v>
+        <v>2.339321190843585</v>
       </c>
       <c r="D24" t="n">
-        <v>14.17592323521591</v>
+        <v>2.303587525722586</v>
       </c>
       <c r="E24" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F24" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>10.52387229655414</v>
+        <v>1.710129248190048</v>
       </c>
       <c r="D25" t="n">
-        <v>10.787414404152</v>
+        <v>1.7529548406747</v>
       </c>
       <c r="E25" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F25" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>36.44195176426233</v>
+        <v>5.92181716169263</v>
       </c>
       <c r="D26" t="n">
-        <v>36.53419066726257</v>
+        <v>5.936805983430168</v>
       </c>
       <c r="E26" t="n">
-        <v>8.429592854648615</v>
+        <v>1.3698088388804</v>
       </c>
       <c r="F26" t="n">
-        <v>12.8311620036894</v>
+        <v>2.085063825599528</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
